--- a/Design-Files/Deliverables/BOM/eSpark BOM.xlsx
+++ b/Design-Files/Deliverables/BOM/eSpark BOM.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\hasanmehmood-motordriver\Design-Files\Deliverables\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9144"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9150"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="335">
   <si>
     <t>Component list</t>
   </si>
@@ -974,22 +979,63 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>WJ15EDGK-3.81-8P</t>
+  </si>
+  <si>
+    <t>8 1 3.81mm 1x8P Green Plug P=3.81mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ningbo </t>
+  </si>
+  <si>
+    <t>C14234</t>
+  </si>
+  <si>
+    <t>WJ15EDGK-3.81-12P</t>
+  </si>
+  <si>
+    <t>12 1 3.81mm 1x12P Green Plug P=3.81mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>C18980</t>
+  </si>
+  <si>
+    <t>021806.3HXP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t>C3156688</t>
+  </si>
+  <si>
+    <t>63A Glass Tube Fuse 6.3A 250V - Fuses</t>
+  </si>
+  <si>
+    <t>RF Module</t>
+  </si>
+  <si>
+    <t>High sensitivity wireless remote control receiving module RXB61 multiple frequency 315M.433MHZ</t>
+  </si>
+  <si>
+    <t>Alibaba</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="7">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="3">
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1142,7 +1188,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1166,144 +1211,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1328,194 +1237,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="29">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1747,253 +1470,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2025,15 +1509,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2064,7 +1542,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2133,23 +1611,50 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="17" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="17" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2159,120 +1664,50 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0003A4CB"/>
-      <color rgb="002CD0B2"/>
+      <color rgb="FF03A4CB"/>
+      <color rgb="FF2CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>18</xdr:col>
@@ -2294,7 +1729,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2573,36 +2008,37 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S65"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="3.13888888888889" style="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.4259259259259" customWidth="1"/>
-    <col min="5" max="5" width="30.8518518518519" customWidth="1"/>
-    <col min="6" max="6" width="22.287037037037" customWidth="1"/>
-    <col min="7" max="7" width="33.4259259259259" customWidth="1"/>
-    <col min="8" max="8" width="21.4259259259259" customWidth="1"/>
-    <col min="9" max="9" width="29.712962962963" customWidth="1"/>
-    <col min="10" max="10" width="17.8888888888889" customWidth="1"/>
-    <col min="11" max="11" width="8.22222222222222" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="29.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="15.7777777777778" customWidth="1"/>
-    <col min="15" max="15" width="5.88888888888889" customWidth="1"/>
-    <col min="16" max="16" width="19.4444444444444" customWidth="1"/>
-    <col min="17" max="17" width="20.1111111111111" customWidth="1"/>
-    <col min="18" max="18" width="16.5740740740741" customWidth="1"/>
-    <col min="19" max="19" width="26.8518518518519" customWidth="1"/>
+    <col min="14" max="14" width="15.7109375" customWidth="1"/>
+    <col min="15" max="15" width="5.85546875" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" customWidth="1"/>
+    <col min="18" max="18" width="16.5703125" customWidth="1"/>
+    <col min="19" max="19" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.15" spans="1:19">
+    <row r="1" spans="1:19">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2613,17 +2049,17 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="61"/>
-    </row>
-    <row r="2" ht="31.95" spans="1:19">
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="65"/>
+    </row>
+    <row r="2" spans="1:19" ht="31.5">
       <c r="A2" s="2"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -2631,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="61" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="8"/>
@@ -2646,7 +2082,7 @@
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
-      <c r="S2" s="62"/>
+      <c r="S2" s="56"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="2"/>
@@ -2656,22 +2092,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="74" t="s">
+      <c r="F3" s="62" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="12"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="12"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="63"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="68"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="2"/>
@@ -2681,22 +2117,22 @@
         <v>4</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="74" t="s">
+      <c r="F4" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="64"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="69"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="2"/>
@@ -2706,3046 +2142,3273 @@
         <v>5</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="75" t="s">
+      <c r="F5" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="64"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="69"/>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="2"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="64"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="69"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="2"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="64"/>
-    </row>
-    <row r="8" ht="15.15" spans="1:19">
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="69"/>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="2"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="64"/>
-    </row>
-    <row r="9" ht="15.15" spans="1:19">
+      <c r="B8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="69"/>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="2"/>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="I9" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="33" t="s">
+      <c r="K9" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="33" t="s">
+      <c r="L9" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="33" t="s">
+      <c r="M9" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="33" t="s">
+      <c r="N9" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="O9" s="33" t="s">
+      <c r="O9" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="P9" s="33" t="s">
+      <c r="P9" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="Q9" s="33" t="s">
+      <c r="Q9" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="R9" s="33" t="s">
+      <c r="R9" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="S9" s="33" t="s">
+      <c r="S9" s="31" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" ht="24" spans="1:19">
+    <row r="10" spans="1:19" ht="24">
       <c r="A10" s="2"/>
-      <c r="B10" s="34">
+      <c r="B10" s="32">
         <f t="shared" ref="B10:B17" si="0">ROW(B10)-ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="36" t="s">
+      <c r="I10" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="K10" s="36" t="s">
+      <c r="K10" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="36">
+      <c r="L10" s="34">
         <v>1</v>
       </c>
-      <c r="M10" s="36">
+      <c r="M10" s="34">
         <f t="shared" ref="M10:M17" si="1">L10*5</f>
         <v>5</v>
       </c>
-      <c r="N10" s="36">
+      <c r="N10" s="34">
         <v>10</v>
       </c>
-      <c r="O10" s="54" t="s">
+      <c r="O10" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P10" s="55">
-        <v>0.0347</v>
-      </c>
-      <c r="Q10" s="55">
+      <c r="P10" s="52">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="Q10" s="52">
         <f t="shared" ref="Q10:Q17" si="2">P10*N10</f>
-        <v>0.347</v>
-      </c>
-      <c r="R10" s="36"/>
-      <c r="S10" s="65"/>
+        <v>0.34700000000000003</v>
+      </c>
+      <c r="R10" s="34"/>
+      <c r="S10" s="57"/>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="2"/>
-      <c r="B11" s="37">
+      <c r="B11" s="35">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="G11" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="39" t="s">
+      <c r="H11" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="39" t="s">
+      <c r="I11" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="39" t="s">
+      <c r="K11" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="L11" s="39">
+      <c r="L11" s="37">
         <v>5</v>
       </c>
-      <c r="M11" s="39">
+      <c r="M11" s="37">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="N11" s="39">
+      <c r="N11" s="37">
         <v>100</v>
       </c>
-      <c r="O11" s="56" t="s">
+      <c r="O11" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="57">
-        <v>0.0034</v>
-      </c>
-      <c r="Q11" s="57">
+      <c r="P11" s="54">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="Q11" s="54">
         <f t="shared" si="2"/>
-        <v>0.34</v>
-      </c>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-    </row>
-    <row r="12" ht="36" spans="1:19">
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="R11" s="37"/>
+      <c r="S11" s="37"/>
+    </row>
+    <row r="12" spans="1:19" ht="36">
       <c r="A12" s="2"/>
-      <c r="B12" s="34">
+      <c r="B12" s="32">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="36" t="s">
+      <c r="H12" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="36" t="s">
+      <c r="I12" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="K12" s="36" t="s">
+      <c r="K12" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="L12" s="36">
+      <c r="L12" s="34">
         <v>1</v>
       </c>
-      <c r="M12" s="36">
+      <c r="M12" s="34">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N12" s="36">
+      <c r="N12" s="34">
         <v>10</v>
       </c>
-      <c r="O12" s="54" t="s">
+      <c r="O12" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P12" s="55">
-        <v>0.0716</v>
-      </c>
-      <c r="Q12" s="55">
+      <c r="P12" s="52">
+        <v>7.1599999999999997E-2</v>
+      </c>
+      <c r="Q12" s="52">
         <f t="shared" si="2"/>
-        <v>0.716</v>
-      </c>
-      <c r="R12" s="36"/>
-      <c r="S12" s="65"/>
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="R12" s="34"/>
+      <c r="S12" s="57"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="2"/>
-      <c r="B13" s="37">
+      <c r="B13" s="35">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="39" t="s">
+      <c r="H13" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="J13" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="K13" s="39" t="s">
+      <c r="K13" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="L13" s="39">
+      <c r="L13" s="37">
         <v>3</v>
       </c>
-      <c r="M13" s="39">
+      <c r="M13" s="37">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="N13" s="39">
+      <c r="N13" s="37">
         <v>20</v>
       </c>
-      <c r="O13" s="56" t="s">
+      <c r="O13" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P13" s="57">
-        <v>0.0239</v>
-      </c>
-      <c r="Q13" s="57">
+      <c r="P13" s="54">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="Q13" s="54">
         <f t="shared" si="2"/>
-        <v>0.478</v>
-      </c>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-    </row>
-    <row r="14" ht="24" spans="1:19">
+        <v>0.47800000000000004</v>
+      </c>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
+    </row>
+    <row r="14" spans="1:19" ht="24">
       <c r="A14" s="2"/>
-      <c r="B14" s="34">
+      <c r="B14" s="32">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="36" t="s">
+      <c r="H14" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="36" t="s">
+      <c r="I14" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="K14" s="36" t="s">
+      <c r="K14" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="L14" s="36">
+      <c r="L14" s="34">
         <v>1</v>
       </c>
-      <c r="M14" s="36">
+      <c r="M14" s="34">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N14" s="36">
+      <c r="N14" s="34">
         <v>100</v>
       </c>
-      <c r="O14" s="54" t="s">
+      <c r="O14" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P14" s="55">
-        <v>0.0027</v>
-      </c>
-      <c r="Q14" s="55">
+      <c r="P14" s="52">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="Q14" s="52">
         <f t="shared" si="2"/>
         <v>0.27</v>
       </c>
-      <c r="R14" s="36"/>
-      <c r="S14" s="65"/>
-    </row>
-    <row r="15" ht="36" spans="1:19">
+      <c r="R14" s="34"/>
+      <c r="S14" s="57"/>
+    </row>
+    <row r="15" spans="1:19" ht="36">
       <c r="A15" s="2"/>
-      <c r="B15" s="37">
+      <c r="B15" s="35">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="39" t="s">
+      <c r="G15" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="39" t="s">
+      <c r="H15" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="I15" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="39" t="s">
+      <c r="I15" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="39" t="s">
+      <c r="K15" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="L15" s="39">
+      <c r="L15" s="37">
         <v>1</v>
       </c>
-      <c r="M15" s="39">
+      <c r="M15" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N15" s="39">
+      <c r="N15" s="37">
         <v>20</v>
       </c>
-      <c r="O15" s="56" t="s">
+      <c r="O15" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P15" s="57">
-        <v>0.0236</v>
-      </c>
-      <c r="Q15" s="57">
+      <c r="P15" s="54">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="Q15" s="54">
         <f t="shared" si="2"/>
-        <v>0.472</v>
-      </c>
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="R15" s="37"/>
+      <c r="S15" s="37"/>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="2"/>
-      <c r="B16" s="34">
+      <c r="B16" s="32">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="36" t="s">
+      <c r="F16" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="36" t="s">
+      <c r="G16" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="36" t="s">
+      <c r="H16" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="I16" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="36" t="s">
+      <c r="I16" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="K16" s="36" t="s">
+      <c r="K16" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="L16" s="36">
+      <c r="L16" s="34">
         <v>6</v>
       </c>
-      <c r="M16" s="36">
+      <c r="M16" s="34">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N16" s="36">
+      <c r="N16" s="34">
         <v>35</v>
       </c>
-      <c r="O16" s="54" t="s">
+      <c r="O16" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P16" s="55">
-        <v>0.0886</v>
-      </c>
-      <c r="Q16" s="55">
+      <c r="P16" s="52">
+        <v>8.8599999999999998E-2</v>
+      </c>
+      <c r="Q16" s="52">
         <f t="shared" si="2"/>
         <v>3.101</v>
       </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="65"/>
-    </row>
-    <row r="17" ht="24" spans="1:19">
+      <c r="R16" s="34"/>
+      <c r="S16" s="57"/>
+    </row>
+    <row r="17" spans="1:19" ht="24">
       <c r="A17" s="2"/>
-      <c r="B17" s="37">
+      <c r="B17" s="35">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="39" t="s">
+      <c r="H17" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="I17" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="39" t="s">
+      <c r="I17" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="L17" s="39">
+      <c r="L17" s="37">
         <v>1</v>
       </c>
-      <c r="M17" s="39">
+      <c r="M17" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N17" s="39">
+      <c r="N17" s="37">
         <v>20</v>
       </c>
-      <c r="O17" s="56" t="s">
+      <c r="O17" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P17" s="57">
-        <v>0.0304</v>
-      </c>
-      <c r="Q17" s="57">
+      <c r="P17" s="54">
+        <v>3.04E-2</v>
+      </c>
+      <c r="Q17" s="54">
         <f t="shared" si="2"/>
-        <v>0.608</v>
-      </c>
-      <c r="R17" s="39"/>
-      <c r="S17" s="39"/>
-    </row>
-    <row r="18" ht="24" spans="1:19">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="R17" s="37"/>
+      <c r="S17" s="37"/>
+    </row>
+    <row r="18" spans="1:19" ht="24">
       <c r="A18" s="2"/>
-      <c r="B18" s="37">
-        <f t="shared" ref="B18:B59" si="3">ROW(B18)-ROW($B$9)</f>
+      <c r="B18" s="35">
+        <f t="shared" ref="B18:B63" si="3">ROW(B18)-ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="39" t="s">
+      <c r="H18" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="I18" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="39" t="s">
+      <c r="I18" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="K18" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L18" s="39">
+      <c r="K18" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="37">
         <v>3</v>
       </c>
-      <c r="M18" s="39">
-        <f t="shared" ref="M18:M59" si="4">L18*5</f>
+      <c r="M18" s="37">
+        <f t="shared" ref="M18:M63" si="4">L18*5</f>
         <v>15</v>
       </c>
-      <c r="N18" s="39">
+      <c r="N18" s="37">
         <v>50</v>
       </c>
-      <c r="O18" s="56" t="s">
+      <c r="O18" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P18" s="57">
-        <v>0.0088</v>
-      </c>
-      <c r="Q18" s="57">
-        <f t="shared" ref="Q18:Q59" si="5">P18*N18</f>
+      <c r="P18" s="54">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="Q18" s="54">
+        <f t="shared" ref="Q18:Q63" si="5">P18*N18</f>
         <v>0.44</v>
       </c>
-      <c r="R18" s="39"/>
-      <c r="S18" s="39"/>
+      <c r="R18" s="37"/>
+      <c r="S18" s="37"/>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="2"/>
-      <c r="B19" s="34">
+      <c r="B19" s="32">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="36" t="s">
+      <c r="H19" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I19" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="36" t="s">
+      <c r="I19" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="K19" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L19" s="36">
+      <c r="K19" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="34">
         <v>1</v>
       </c>
-      <c r="M19" s="36">
+      <c r="M19" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N19" s="36">
+      <c r="N19" s="34">
         <v>10</v>
       </c>
-      <c r="O19" s="54" t="s">
+      <c r="O19" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P19" s="55">
+      <c r="P19" s="52">
         <v>0.1784</v>
       </c>
-      <c r="Q19" s="55">
+      <c r="Q19" s="52">
         <f t="shared" si="5"/>
         <v>1.784</v>
       </c>
-      <c r="R19" s="36"/>
-      <c r="S19" s="65"/>
-    </row>
-    <row r="20" ht="36" spans="1:19">
+      <c r="R19" s="34"/>
+      <c r="S19" s="57"/>
+    </row>
+    <row r="20" spans="1:19" ht="36">
       <c r="A20" s="2"/>
-      <c r="B20" s="37">
+      <c r="B20" s="35">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="H20" s="39" t="s">
+      <c r="H20" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="I20" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="39" t="s">
+      <c r="I20" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="K20" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L20" s="39">
+      <c r="K20" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="37">
         <v>18</v>
       </c>
-      <c r="M20" s="39">
+      <c r="M20" s="37">
         <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="N20" s="39">
+      <c r="N20" s="37">
         <v>100</v>
       </c>
-      <c r="O20" s="56" t="s">
+      <c r="O20" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P20" s="57">
-        <v>0.0121</v>
-      </c>
-      <c r="Q20" s="57">
+      <c r="P20" s="54">
+        <v>1.21E-2</v>
+      </c>
+      <c r="Q20" s="54">
         <f t="shared" si="5"/>
         <v>1.21</v>
       </c>
-      <c r="R20" s="39"/>
-      <c r="S20" s="39"/>
-    </row>
-    <row r="21" ht="48" spans="1:19">
+      <c r="R20" s="37"/>
+      <c r="S20" s="37"/>
+    </row>
+    <row r="21" spans="1:19" ht="60">
       <c r="A21" s="2"/>
-      <c r="B21" s="34">
+      <c r="B21" s="32">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="H21" s="36" t="s">
+      <c r="H21" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="I21" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="36" t="s">
+      <c r="I21" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36">
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
         <v>1</v>
       </c>
-      <c r="M21" s="36">
+      <c r="M21" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N21" s="36">
+      <c r="N21" s="34">
         <v>10</v>
       </c>
-      <c r="O21" s="54" t="s">
+      <c r="O21" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P21" s="55">
-        <v>0.2446</v>
-      </c>
-      <c r="Q21" s="55">
+      <c r="P21" s="52">
+        <v>0.24460000000000001</v>
+      </c>
+      <c r="Q21" s="52">
         <f t="shared" si="5"/>
-        <v>2.446</v>
-      </c>
-      <c r="R21" s="36"/>
-      <c r="S21" s="65"/>
-    </row>
-    <row r="22" ht="48" spans="1:19">
+        <v>2.4460000000000002</v>
+      </c>
+      <c r="R21" s="34"/>
+      <c r="S21" s="57"/>
+    </row>
+    <row r="22" spans="1:19" ht="60">
       <c r="A22" s="2"/>
-      <c r="B22" s="37">
+      <c r="B22" s="35">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="39" t="s">
+      <c r="E22" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="36" t="s">
+      <c r="F22" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="39" t="s">
+      <c r="G22" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="H22" s="39" t="s">
+      <c r="H22" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="I22" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="39" t="s">
+      <c r="I22" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39">
+      <c r="K22" s="37"/>
+      <c r="L22" s="37">
         <v>1</v>
       </c>
-      <c r="M22" s="39">
+      <c r="M22" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N22" s="39">
+      <c r="N22" s="37">
         <v>6</v>
       </c>
-      <c r="O22" s="56" t="s">
+      <c r="O22" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P22" s="57">
-        <v>0.4296</v>
-      </c>
-      <c r="Q22" s="57">
+      <c r="P22" s="54">
+        <v>0.42959999999999998</v>
+      </c>
+      <c r="Q22" s="54">
         <f t="shared" si="5"/>
-        <v>2.5776</v>
-      </c>
-      <c r="R22" s="39"/>
-      <c r="S22" s="39"/>
-    </row>
-    <row r="23" ht="24" spans="1:19">
+        <v>2.5775999999999999</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="37"/>
+    </row>
+    <row r="23" spans="1:19" ht="24">
       <c r="A23" s="2"/>
-      <c r="B23" s="34">
+      <c r="B23" s="32">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="E23" s="36" t="s">
+      <c r="E23" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="36" t="s">
+      <c r="G23" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="H23" s="36" t="s">
+      <c r="H23" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="I23" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="36" t="s">
+      <c r="I23" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36">
+      <c r="K23" s="34"/>
+      <c r="L23" s="34">
         <v>1</v>
       </c>
-      <c r="M23" s="36">
+      <c r="M23" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N23" s="36">
+      <c r="N23" s="34">
         <v>20</v>
       </c>
-      <c r="O23" s="54" t="s">
+      <c r="O23" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P23" s="55">
-        <v>0.024</v>
-      </c>
-      <c r="Q23" s="55">
+      <c r="P23" s="52">
+        <v>2.4E-2</v>
+      </c>
+      <c r="Q23" s="52">
         <f t="shared" si="5"/>
         <v>0.48</v>
       </c>
-      <c r="R23" s="36"/>
-      <c r="S23" s="65"/>
-    </row>
-    <row r="24" ht="36" spans="1:19">
+      <c r="R23" s="34"/>
+      <c r="S23" s="57"/>
+    </row>
+    <row r="24" spans="1:19" ht="48">
       <c r="A24" s="2"/>
-      <c r="B24" s="37">
+      <c r="B24" s="35">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="F24" s="39" t="s">
+      <c r="F24" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="39" t="s">
+      <c r="G24" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="H24" s="39" t="s">
+      <c r="H24" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="I24" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="39" t="s">
+      <c r="I24" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39">
+      <c r="K24" s="37"/>
+      <c r="L24" s="37">
         <v>1</v>
       </c>
-      <c r="M24" s="39">
+      <c r="M24" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N24" s="39">
+      <c r="N24" s="37">
         <v>10</v>
       </c>
-      <c r="O24" s="56" t="s">
+      <c r="O24" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P24" s="57">
-        <v>0.0369</v>
-      </c>
-      <c r="Q24" s="57">
+      <c r="P24" s="54">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="Q24" s="54">
         <f t="shared" si="5"/>
-        <v>0.369</v>
-      </c>
-      <c r="R24" s="39"/>
-      <c r="S24" s="39"/>
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="37"/>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="2"/>
-      <c r="B25" s="34">
+      <c r="B25" s="32">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="C25" s="35" t="s">
+      <c r="C25" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="36" t="s">
+      <c r="E25" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="G25" s="41" t="s">
+      <c r="G25" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="H25" s="36" t="s">
+      <c r="H25" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="I25" s="36" t="s">
+      <c r="I25" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="J25" s="36" t="s">
+      <c r="J25" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36">
+      <c r="K25" s="34"/>
+      <c r="L25" s="34">
         <v>1</v>
       </c>
-      <c r="M25" s="36">
+      <c r="M25" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N25" s="36">
+      <c r="N25" s="34">
         <v>10</v>
       </c>
-      <c r="O25" s="54" t="s">
+      <c r="O25" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P25" s="55">
-        <v>0.0493</v>
-      </c>
-      <c r="Q25" s="55">
+      <c r="P25" s="52">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="Q25" s="52">
         <f t="shared" si="5"/>
-        <v>0.493</v>
-      </c>
-      <c r="R25" s="36"/>
-      <c r="S25" s="65"/>
-    </row>
-    <row r="26" ht="24" spans="1:19">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="R25" s="34"/>
+      <c r="S25" s="57"/>
+    </row>
+    <row r="26" spans="1:19" ht="24">
       <c r="A26" s="2"/>
-      <c r="B26" s="37">
+      <c r="B26" s="35">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="39" t="s">
+      <c r="E26" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="F26" s="39" t="s">
+      <c r="F26" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="G26" s="39" t="s">
+      <c r="G26" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="H26" s="39" t="s">
+      <c r="H26" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="I26" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26" s="39" t="s">
+      <c r="I26" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="K26" s="39"/>
-      <c r="L26" s="39">
+      <c r="K26" s="37"/>
+      <c r="L26" s="37">
         <v>1</v>
       </c>
-      <c r="M26" s="39">
+      <c r="M26" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N26" s="39">
+      <c r="N26" s="37">
         <v>20</v>
       </c>
-      <c r="O26" s="56" t="s">
+      <c r="O26" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P26" s="57">
-        <v>0.024</v>
-      </c>
-      <c r="Q26" s="57">
+      <c r="P26" s="54">
+        <v>2.4E-2</v>
+      </c>
+      <c r="Q26" s="54">
         <f t="shared" si="5"/>
         <v>0.48</v>
       </c>
-      <c r="R26" s="39"/>
-      <c r="S26" s="39"/>
-    </row>
-    <row r="27" ht="36" spans="1:19">
+      <c r="R26" s="37"/>
+      <c r="S26" s="37"/>
+    </row>
+    <row r="27" spans="1:19" ht="48">
       <c r="A27" s="2"/>
-      <c r="B27" s="34">
+      <c r="B27" s="32">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="E27" s="41" t="s">
+      <c r="E27" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="41" t="s">
+      <c r="F27" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="G27" s="41" t="s">
+      <c r="G27" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="H27" s="41" t="s">
+      <c r="H27" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="I27" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="J27" s="41" t="s">
+      <c r="I27" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="K27" s="41" t="s">
+      <c r="K27" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="L27" s="41">
+      <c r="L27" s="39">
         <v>1</v>
       </c>
-      <c r="M27" s="41">
+      <c r="M27" s="39">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N27" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="O27" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="P27" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q27" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="R27" s="42" t="s">
+      <c r="N27" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O27" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P27" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q27" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="R27" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="S27" s="66"/>
-    </row>
-    <row r="28" ht="24" spans="1:19">
+      <c r="S27" s="58"/>
+    </row>
+    <row r="28" spans="1:19" ht="24">
       <c r="A28" s="2"/>
-      <c r="B28" s="37">
+      <c r="B28" s="35">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="D28" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="E28" s="39" t="s">
+      <c r="E28" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="F28" s="39" t="s">
+      <c r="F28" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="39" t="s">
+      <c r="G28" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H28" s="39" t="s">
+      <c r="H28" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="I28" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J28" s="39" t="s">
+      <c r="I28" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="K28" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L28" s="39">
+      <c r="K28" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" s="37">
         <v>1</v>
       </c>
-      <c r="M28" s="39">
+      <c r="M28" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N28" s="39">
+      <c r="N28" s="37">
         <v>6</v>
       </c>
-      <c r="O28" s="56" t="s">
+      <c r="O28" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P28" s="57">
-        <v>0.8035</v>
-      </c>
-      <c r="Q28" s="57">
+      <c r="P28" s="54">
+        <v>0.80349999999999999</v>
+      </c>
+      <c r="Q28" s="54">
         <f t="shared" si="5"/>
-        <v>4.821</v>
-      </c>
-      <c r="R28" s="39"/>
-      <c r="S28" s="39"/>
-    </row>
-    <row r="29" ht="24" spans="1:19">
+        <v>4.8209999999999997</v>
+      </c>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
+    </row>
+    <row r="29" spans="1:19" ht="36">
       <c r="A29" s="2"/>
-      <c r="B29" s="34">
+      <c r="B29" s="32">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="41" t="s">
+      <c r="D29" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="F29" s="41" t="s">
+      <c r="F29" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="G29" s="41" t="s">
+      <c r="G29" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="H29" s="41" t="s">
+      <c r="H29" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="I29" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="41" t="s">
+      <c r="I29" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="K29" s="41" t="s">
+      <c r="K29" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="L29" s="41">
+      <c r="L29" s="39">
         <v>2</v>
       </c>
-      <c r="M29" s="41">
+      <c r="M29" s="39">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N29" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="O29" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="P29" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q29" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="R29" s="42" t="s">
+      <c r="N29" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O29" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P29" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q29" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="R29" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="S29" s="66"/>
-    </row>
-    <row r="30" ht="36" spans="1:19">
+      <c r="S29" s="58"/>
+    </row>
+    <row r="30" spans="1:19" ht="48">
       <c r="A30" s="2"/>
-      <c r="B30" s="37">
+      <c r="B30" s="35">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="39" t="s">
+      <c r="D30" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="E30" s="39" t="s">
+      <c r="E30" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="39" t="s">
+      <c r="F30" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="39" t="s">
+      <c r="G30" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="H30" s="39" t="s">
+      <c r="H30" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="I30" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" s="39" t="s">
+      <c r="I30" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="K30" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L30" s="39">
+      <c r="K30" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30" s="37">
         <v>1</v>
       </c>
-      <c r="M30" s="39">
+      <c r="M30" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N30" s="39">
+      <c r="N30" s="37">
         <v>10</v>
       </c>
-      <c r="O30" s="56" t="s">
+      <c r="O30" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P30" s="57">
+      <c r="P30" s="54">
         <v>0.1704</v>
       </c>
-      <c r="Q30" s="57">
+      <c r="Q30" s="54">
         <f t="shared" si="5"/>
         <v>1.704</v>
       </c>
-      <c r="R30" s="39"/>
-      <c r="S30" s="39"/>
-    </row>
-    <row r="31" ht="36" spans="1:19">
+      <c r="R30" s="37"/>
+      <c r="S30" s="37"/>
+    </row>
+    <row r="31" spans="1:19" ht="36">
       <c r="A31" s="2"/>
-      <c r="B31" s="34">
+      <c r="B31" s="32">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="E31" s="36" t="s">
+      <c r="E31" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="39" t="s">
+      <c r="F31" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="36" t="s">
+      <c r="G31" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="H31" s="36" t="s">
+      <c r="H31" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="I31" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" s="36" t="s">
+      <c r="I31" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="K31" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="36">
+      <c r="K31" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="34">
         <v>1</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="34">
         <v>20</v>
       </c>
-      <c r="O31" s="54" t="s">
+      <c r="O31" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P31" s="55">
-        <v>0.0317</v>
-      </c>
-      <c r="Q31" s="55">
+      <c r="P31" s="52">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="Q31" s="52">
         <f t="shared" si="5"/>
-        <v>0.634</v>
-      </c>
-      <c r="R31" s="36"/>
-      <c r="S31" s="65"/>
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="R31" s="34"/>
+      <c r="S31" s="57"/>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="2"/>
-      <c r="B32" s="37">
+      <c r="B32" s="35">
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="D32" s="39" t="s">
+      <c r="D32" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="E32" s="39" t="s">
+      <c r="E32" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G32" s="39" t="s">
+      <c r="G32" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H32" s="39" t="s">
+      <c r="H32" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="I32" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="39" t="s">
+      <c r="I32" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="K32" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L32" s="39">
+      <c r="K32" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="37">
         <v>3</v>
       </c>
-      <c r="M32" s="39">
+      <c r="M32" s="37">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="N32" s="39">
+      <c r="N32" s="37">
         <v>16</v>
       </c>
-      <c r="O32" s="56" t="s">
+      <c r="O32" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P32" s="57">
+      <c r="P32" s="54">
         <v>1.3714</v>
       </c>
-      <c r="Q32" s="57">
+      <c r="Q32" s="54">
         <f t="shared" si="5"/>
-        <v>21.9424</v>
-      </c>
-      <c r="R32" s="39"/>
-      <c r="S32" s="39"/>
-    </row>
-    <row r="33" ht="24" spans="1:19">
+        <v>21.942399999999999</v>
+      </c>
+      <c r="R32" s="37"/>
+      <c r="S32" s="37"/>
+    </row>
+    <row r="33" spans="1:19" ht="24">
       <c r="A33" s="2"/>
-      <c r="B33" s="34">
+      <c r="B33" s="32">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="C33" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="E33" s="36" t="s">
+      <c r="E33" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="G33" s="36" t="s">
+      <c r="G33" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="H33" s="36" t="s">
+      <c r="H33" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="I33" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" s="36" t="s">
+      <c r="I33" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="K33" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L33" s="36">
+      <c r="K33" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="34">
         <v>8</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="34">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="34">
         <v>60</v>
       </c>
-      <c r="O33" s="54" t="s">
+      <c r="O33" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P33" s="55">
-        <v>0.0313</v>
-      </c>
-      <c r="Q33" s="55">
+      <c r="P33" s="52">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="Q33" s="52">
         <f t="shared" si="5"/>
-        <v>1.878</v>
-      </c>
-      <c r="R33" s="36"/>
-      <c r="S33" s="65"/>
-    </row>
-    <row r="34" ht="24" spans="1:19">
+        <v>1.8780000000000001</v>
+      </c>
+      <c r="R33" s="34"/>
+      <c r="S33" s="57"/>
+    </row>
+    <row r="34" spans="1:19" ht="24">
       <c r="A34" s="2"/>
-      <c r="B34" s="37">
+      <c r="B34" s="35">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C34" s="38" t="s">
+      <c r="C34" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="D34" s="39" t="s">
+      <c r="D34" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="E34" s="39" t="s">
+      <c r="E34" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="F34" s="39" t="s">
+      <c r="F34" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="G34" s="39" t="s">
+      <c r="G34" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="H34" s="39" t="s">
+      <c r="H34" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="I34" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" s="39" t="s">
+      <c r="I34" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="K34" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L34" s="39">
+      <c r="K34" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34" s="37">
         <v>2</v>
       </c>
-      <c r="M34" s="39">
+      <c r="M34" s="37">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N34" s="39">
+      <c r="N34" s="37">
         <v>11</v>
       </c>
-      <c r="O34" s="56" t="s">
+      <c r="O34" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P34" s="57">
-        <v>0.6237</v>
-      </c>
-      <c r="Q34" s="57">
+      <c r="P34" s="54">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="Q34" s="54">
         <f t="shared" si="5"/>
-        <v>6.8607</v>
-      </c>
-      <c r="R34" s="39"/>
-      <c r="S34" s="39"/>
-    </row>
-    <row r="35" ht="24" spans="1:19">
+        <v>6.8607000000000005</v>
+      </c>
+      <c r="R34" s="37"/>
+      <c r="S34" s="37"/>
+    </row>
+    <row r="35" spans="1:19" ht="36">
       <c r="A35" s="2"/>
-      <c r="B35" s="34">
+      <c r="B35" s="32">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="E35" s="36" t="s">
+      <c r="E35" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="F35" s="36" t="s">
+      <c r="F35" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="H35" s="36" t="s">
+      <c r="H35" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="I35" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J35" s="36" t="s">
+      <c r="I35" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="K35" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L35" s="36">
+      <c r="K35" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" s="34">
         <v>4</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="34">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="34">
         <v>50</v>
       </c>
-      <c r="O35" s="54" t="s">
+      <c r="O35" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P35" s="55">
-        <v>0.0143</v>
-      </c>
-      <c r="Q35" s="55">
+      <c r="P35" s="52">
+        <v>1.43E-2</v>
+      </c>
+      <c r="Q35" s="52">
         <f t="shared" si="5"/>
-        <v>0.715</v>
-      </c>
-      <c r="R35" s="36"/>
-      <c r="S35" s="65"/>
-    </row>
-    <row r="36" ht="27.6" spans="1:19">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="R35" s="34"/>
+      <c r="S35" s="57"/>
+    </row>
+    <row r="36" spans="1:19" ht="36">
       <c r="A36" s="2"/>
-      <c r="B36" s="37">
+      <c r="B36" s="35">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
-      <c r="C36" s="35" t="s">
+      <c r="C36" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="D36" s="39" t="s">
+      <c r="D36" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="E36" s="39" t="s">
+      <c r="E36" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="F36" s="39" t="s">
+      <c r="F36" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="H36" s="39" t="s">
+      <c r="H36" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I36" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="39" t="s">
+      <c r="I36" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="K36" s="39" t="s">
+      <c r="K36" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="L36" s="39">
+      <c r="L36" s="37">
         <v>4</v>
       </c>
-      <c r="M36" s="39">
+      <c r="M36" s="37">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N36" s="39">
+      <c r="N36" s="37">
         <v>40</v>
       </c>
-      <c r="O36" s="56" t="s">
+      <c r="O36" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P36" s="57">
-        <v>0.0295</v>
-      </c>
-      <c r="Q36" s="57">
+      <c r="P36" s="54">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="Q36" s="54">
         <f t="shared" si="5"/>
         <v>1.18</v>
       </c>
-      <c r="R36" s="39"/>
-      <c r="S36" s="39"/>
-    </row>
-    <row r="37" ht="27.6" spans="1:19">
+      <c r="R36" s="37"/>
+      <c r="S36" s="37"/>
+    </row>
+    <row r="37" spans="1:19" ht="25.5">
       <c r="A37" s="2"/>
-      <c r="B37" s="34">
+      <c r="B37" s="32">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E37" s="36" t="s">
+      <c r="E37" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="F37" s="36" t="s">
+      <c r="F37" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G37" s="36" t="s">
+      <c r="G37" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="H37" s="36" t="s">
+      <c r="H37" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I37" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J37" s="36" t="s">
+      <c r="I37" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="K37" s="36" t="s">
+      <c r="K37" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="34">
         <v>2</v>
       </c>
-      <c r="M37" s="36">
+      <c r="M37" s="34">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N37" s="36">
+      <c r="N37" s="34">
         <v>50</v>
       </c>
-      <c r="O37" s="54" t="s">
+      <c r="O37" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P37" s="55">
-        <v>0.0186</v>
-      </c>
-      <c r="Q37" s="55">
+      <c r="P37" s="52">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="Q37" s="52">
         <f t="shared" si="5"/>
-        <v>0.93</v>
-      </c>
-      <c r="R37" s="36"/>
-      <c r="S37" s="65"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="R37" s="34"/>
+      <c r="S37" s="57"/>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="2"/>
-      <c r="B38" s="37">
+      <c r="B38" s="35">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
-      <c r="C38" s="35" t="s">
+      <c r="C38" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="E38" s="39" t="s">
+      <c r="E38" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="F38" s="39" t="s">
+      <c r="F38" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="G38" s="39" t="s">
+      <c r="G38" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="H38" s="39" t="s">
+      <c r="H38" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="I38" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" s="39" t="s">
+      <c r="I38" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="K38" s="39" t="s">
+      <c r="K38" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="L38" s="39">
+      <c r="L38" s="37">
         <v>3</v>
       </c>
-      <c r="M38" s="39">
+      <c r="M38" s="37">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="N38" s="39">
+      <c r="N38" s="37">
         <v>50</v>
       </c>
-      <c r="O38" s="56" t="s">
+      <c r="O38" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P38" s="57">
-        <v>0.0135</v>
-      </c>
-      <c r="Q38" s="57">
+      <c r="P38" s="54">
+        <v>1.35E-2</v>
+      </c>
+      <c r="Q38" s="54">
         <f t="shared" si="5"/>
-        <v>0.675</v>
-      </c>
-      <c r="R38" s="39"/>
-      <c r="S38" s="39"/>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="R38" s="37"/>
+      <c r="S38" s="37"/>
     </row>
     <row r="39" spans="1:19">
       <c r="A39" s="2"/>
-      <c r="B39" s="34">
+      <c r="B39" s="32">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="C39" s="35" t="s">
+      <c r="C39" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="E39" s="36" t="s">
+      <c r="E39" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="F39" s="36" t="s">
+      <c r="F39" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="G39" s="36" t="s">
+      <c r="G39" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="H39" s="36" t="s">
+      <c r="H39" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="I39" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J39" s="36" t="s">
+      <c r="I39" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="K39" s="36" t="s">
+      <c r="K39" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="L39" s="36">
+      <c r="L39" s="34">
         <v>6</v>
       </c>
-      <c r="M39" s="36">
+      <c r="M39" s="34">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="N39" s="36">
+      <c r="N39" s="34">
         <v>100</v>
       </c>
-      <c r="O39" s="54" t="s">
+      <c r="O39" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P39" s="55">
-        <v>0.0012</v>
-      </c>
-      <c r="Q39" s="55">
+      <c r="P39" s="52">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q39" s="52">
         <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
-      <c r="R39" s="36"/>
-      <c r="S39" s="65"/>
+      <c r="R39" s="34"/>
+      <c r="S39" s="57"/>
     </row>
     <row r="40" spans="1:19">
       <c r="A40" s="2"/>
-      <c r="B40" s="37">
+      <c r="B40" s="35">
         <f t="shared" si="3"/>
         <v>31</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="D40" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="E40" s="39" t="s">
+      <c r="E40" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="F40" s="39" t="s">
+      <c r="F40" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="G40" s="39" t="s">
+      <c r="G40" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="H40" s="39" t="s">
+      <c r="H40" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="I40" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J40" s="39" t="s">
+      <c r="I40" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="K40" s="39" t="s">
+      <c r="K40" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="L40" s="39">
+      <c r="L40" s="37">
         <v>4</v>
       </c>
-      <c r="M40" s="39">
+      <c r="M40" s="37">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N40" s="39">
+      <c r="N40" s="37">
         <v>100</v>
       </c>
-      <c r="O40" s="56" t="s">
+      <c r="O40" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P40" s="57">
-        <v>0.001</v>
-      </c>
-      <c r="Q40" s="57">
+      <c r="P40" s="54">
+        <v>1E-3</v>
+      </c>
+      <c r="Q40" s="54">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="R40" s="39"/>
-      <c r="S40" s="39"/>
+      <c r="R40" s="37"/>
+      <c r="S40" s="37"/>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="2"/>
-      <c r="B41" s="34">
+      <c r="B41" s="32">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="D41" s="36" t="s">
+      <c r="D41" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="36" t="s">
+      <c r="E41" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="36" t="s">
+      <c r="F41" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="G41" s="36" t="s">
+      <c r="G41" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="H41" s="36" t="s">
+      <c r="H41" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J41" s="36" t="s">
+      <c r="I41" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="K41" s="36" t="s">
+      <c r="K41" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="L41" s="36">
+      <c r="L41" s="34">
         <v>2</v>
       </c>
-      <c r="M41" s="36">
+      <c r="M41" s="34">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N41" s="36">
+      <c r="N41" s="34">
         <v>20</v>
       </c>
-      <c r="O41" s="54" t="s">
+      <c r="O41" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P41" s="55">
-        <v>0.0264</v>
-      </c>
-      <c r="Q41" s="55">
+      <c r="P41" s="52">
+        <v>2.64E-2</v>
+      </c>
+      <c r="Q41" s="52">
         <f t="shared" si="5"/>
-        <v>0.528</v>
-      </c>
-      <c r="R41" s="36"/>
-      <c r="S41" s="65"/>
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="R41" s="34"/>
+      <c r="S41" s="57"/>
     </row>
     <row r="42" spans="1:19">
       <c r="A42" s="2"/>
-      <c r="B42" s="37">
+      <c r="B42" s="35">
         <f t="shared" si="3"/>
         <v>33</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="E42" s="39" t="s">
+      <c r="E42" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="F42" s="39" t="s">
+      <c r="F42" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="G42" s="39" t="s">
+      <c r="G42" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="H42" s="39" t="s">
+      <c r="H42" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="I42" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J42" s="39" t="s">
+      <c r="I42" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J42" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="K42" s="39" t="s">
+      <c r="K42" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="L42" s="39">
+      <c r="L42" s="37">
         <v>3</v>
       </c>
-      <c r="M42" s="39">
+      <c r="M42" s="37">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="N42" s="39">
+      <c r="N42" s="37">
         <v>100</v>
       </c>
-      <c r="O42" s="56" t="s">
+      <c r="O42" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P42" s="57">
-        <v>0.0012</v>
-      </c>
-      <c r="Q42" s="57">
+      <c r="P42" s="54">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q42" s="54">
         <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
-      <c r="R42" s="39"/>
-      <c r="S42" s="39"/>
+      <c r="R42" s="37"/>
+      <c r="S42" s="37"/>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" s="2"/>
-      <c r="B43" s="34">
+      <c r="B43" s="32">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="C43" s="35" t="s">
+      <c r="C43" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="E43" s="36" t="s">
+      <c r="E43" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="F43" s="36" t="s">
+      <c r="F43" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="G43" s="36" t="s">
+      <c r="G43" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="H43" s="36" t="s">
+      <c r="H43" s="34" t="s">
         <v>223</v>
       </c>
-      <c r="I43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J43" s="36" t="s">
+      <c r="I43" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J43" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="K43" s="36" t="s">
+      <c r="K43" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="L43" s="36">
+      <c r="L43" s="34">
         <v>6</v>
       </c>
-      <c r="M43" s="36">
+      <c r="M43" s="34">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="N43" s="36">
+      <c r="N43" s="34">
         <v>100</v>
       </c>
-      <c r="O43" s="54" t="s">
+      <c r="O43" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P43" s="55">
-        <v>0.0013</v>
-      </c>
-      <c r="Q43" s="55">
+      <c r="P43" s="52">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q43" s="52">
         <f t="shared" si="5"/>
         <v>0.13</v>
       </c>
-      <c r="R43" s="36"/>
-      <c r="S43" s="65"/>
+      <c r="R43" s="34"/>
+      <c r="S43" s="57"/>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" s="2"/>
-      <c r="B44" s="37">
+      <c r="B44" s="35">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="D44" s="39" t="s">
+      <c r="D44" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="E44" s="39" t="s">
+      <c r="E44" s="37" t="s">
         <v>227</v>
       </c>
-      <c r="F44" s="39" t="s">
+      <c r="F44" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="G44" s="39" t="s">
+      <c r="G44" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="H44" s="39" t="s">
+      <c r="H44" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="I44" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J44" s="39" t="s">
+      <c r="I44" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="K44" s="39" t="s">
+      <c r="K44" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="L44" s="39">
+      <c r="L44" s="37">
         <v>2</v>
       </c>
-      <c r="M44" s="39">
+      <c r="M44" s="37">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N44" s="39">
+      <c r="N44" s="37">
         <v>100</v>
       </c>
-      <c r="O44" s="56" t="s">
+      <c r="O44" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P44" s="57">
-        <v>0.0011</v>
-      </c>
-      <c r="Q44" s="57">
+      <c r="P44" s="54">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q44" s="54">
         <f t="shared" si="5"/>
         <v>0.11</v>
       </c>
-      <c r="R44" s="39"/>
-      <c r="S44" s="39"/>
+      <c r="R44" s="37"/>
+      <c r="S44" s="37"/>
     </row>
     <row r="45" spans="1:19">
       <c r="A45" s="2"/>
-      <c r="B45" s="34">
+      <c r="B45" s="32">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="C45" s="35" t="s">
+      <c r="C45" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="36" t="s">
+      <c r="D45" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="E45" s="36" t="s">
+      <c r="E45" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="F45" s="36" t="s">
+      <c r="F45" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="G45" s="36" t="s">
+      <c r="G45" s="34" t="s">
         <v>233</v>
       </c>
-      <c r="H45" s="36" t="s">
+      <c r="H45" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="I45" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J45" s="36" t="s">
+      <c r="I45" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="K45" s="36" t="s">
+      <c r="K45" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="L45" s="36">
+      <c r="L45" s="34">
         <v>3</v>
       </c>
-      <c r="M45" s="36">
+      <c r="M45" s="34">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="N45" s="36">
+      <c r="N45" s="34">
         <v>100</v>
       </c>
-      <c r="O45" s="54" t="s">
+      <c r="O45" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P45" s="55">
-        <v>0.001</v>
-      </c>
-      <c r="Q45" s="55">
+      <c r="P45" s="52">
+        <v>1E-3</v>
+      </c>
+      <c r="Q45" s="52">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="R45" s="36"/>
-      <c r="S45" s="65"/>
+      <c r="R45" s="34"/>
+      <c r="S45" s="57"/>
     </row>
     <row r="46" spans="1:19">
       <c r="A46" s="2"/>
-      <c r="B46" s="37">
+      <c r="B46" s="35">
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C46" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="E46" s="39" t="s">
+      <c r="E46" s="37" t="s">
         <v>237</v>
       </c>
-      <c r="F46" s="39" t="s">
+      <c r="F46" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="G46" s="39" t="s">
+      <c r="G46" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="H46" s="39" t="s">
+      <c r="H46" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="I46" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J46" s="39" t="s">
+      <c r="I46" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" s="37" t="s">
         <v>239</v>
       </c>
-      <c r="K46" s="39" t="s">
+      <c r="K46" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="L46" s="39">
+      <c r="L46" s="37">
         <v>1</v>
       </c>
-      <c r="M46" s="39">
+      <c r="M46" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N46" s="39">
+      <c r="N46" s="37">
         <v>20</v>
       </c>
-      <c r="O46" s="56" t="s">
+      <c r="O46" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P46" s="57">
-        <v>0.0258</v>
-      </c>
-      <c r="Q46" s="57">
+      <c r="P46" s="54">
+        <v>2.58E-2</v>
+      </c>
+      <c r="Q46" s="54">
         <f t="shared" si="5"/>
-        <v>0.516</v>
-      </c>
-      <c r="R46" s="39"/>
-      <c r="S46" s="39"/>
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="R46" s="37"/>
+      <c r="S46" s="37"/>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="2"/>
-      <c r="B47" s="34">
+      <c r="B47" s="32">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="C47" s="35" t="s">
+      <c r="C47" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="D47" s="36" t="s">
+      <c r="D47" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="E47" s="36" t="s">
+      <c r="E47" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="F47" s="36" t="s">
+      <c r="F47" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="G47" s="36" t="s">
+      <c r="G47" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="H47" s="36" t="s">
+      <c r="H47" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="I47" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J47" s="36" t="s">
+      <c r="I47" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="K47" s="36" t="s">
+      <c r="K47" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="L47" s="36">
+      <c r="L47" s="34">
         <v>1</v>
       </c>
-      <c r="M47" s="36">
+      <c r="M47" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N47" s="36">
+      <c r="N47" s="34">
         <v>100</v>
       </c>
-      <c r="O47" s="54" t="s">
+      <c r="O47" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="P47" s="55">
-        <v>0.0012</v>
-      </c>
-      <c r="Q47" s="55">
+      <c r="P47" s="52">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q47" s="52">
         <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
-      <c r="R47" s="36"/>
-      <c r="S47" s="65"/>
+      <c r="R47" s="34"/>
+      <c r="S47" s="57"/>
     </row>
     <row r="48" spans="1:19">
       <c r="A48" s="2"/>
-      <c r="B48" s="37">
+      <c r="B48" s="35">
         <f t="shared" si="3"/>
         <v>39</v>
       </c>
-      <c r="C48" s="38" t="s">
+      <c r="C48" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="D48" s="39" t="s">
+      <c r="D48" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="E48" s="39" t="s">
+      <c r="E48" s="37" t="s">
         <v>248</v>
       </c>
-      <c r="F48" s="39" t="s">
+      <c r="F48" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="G48" s="40" t="s">
+      <c r="G48" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="H48" s="39" t="s">
+      <c r="H48" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="I48" s="39" t="s">
+      <c r="I48" s="37" t="s">
         <v>250</v>
       </c>
-      <c r="J48" s="39" t="s">
+      <c r="J48" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="K48" s="39" t="s">
+      <c r="K48" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="L48" s="39">
+      <c r="L48" s="37">
         <v>6</v>
       </c>
-      <c r="M48" s="39">
+      <c r="M48" s="37">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="N48" s="39">
+      <c r="N48" s="37">
         <v>100</v>
       </c>
-      <c r="O48" s="56" t="s">
+      <c r="O48" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P48" s="57">
-        <v>0.001</v>
-      </c>
-      <c r="Q48" s="57">
+      <c r="P48" s="54">
+        <v>1E-3</v>
+      </c>
+      <c r="Q48" s="54">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="R48" s="39"/>
-      <c r="S48" s="39"/>
-    </row>
-    <row r="49" ht="24" spans="1:19">
+      <c r="R48" s="37"/>
+      <c r="S48" s="37"/>
+    </row>
+    <row r="49" spans="1:19" ht="24">
       <c r="A49" s="2"/>
-      <c r="B49" s="34">
+      <c r="B49" s="32">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="C49" s="35" t="s">
+      <c r="C49" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="D49" s="36" t="s">
+      <c r="D49" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="E49" s="36" t="s">
+      <c r="E49" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="F49" s="36" t="s">
+      <c r="F49" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G49" s="36" t="s">
+      <c r="G49" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="H49" s="36" t="s">
+      <c r="H49" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="I49" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J49" s="36" t="s">
+      <c r="I49" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="34" t="s">
         <v>258</v>
       </c>
-      <c r="K49" s="36" t="s">
+      <c r="K49" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="L49" s="36">
+      <c r="L49" s="34">
         <v>2</v>
       </c>
-      <c r="M49" s="36">
+      <c r="M49" s="34">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N49" s="36">
+      <c r="N49" s="34">
         <v>15</v>
       </c>
-      <c r="O49" s="54" t="s">
+      <c r="O49" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P49" s="55">
+      <c r="P49" s="52">
         <v>0.1555</v>
       </c>
-      <c r="Q49" s="55">
+      <c r="Q49" s="52">
         <f t="shared" si="5"/>
         <v>2.3325</v>
       </c>
-      <c r="R49" s="36"/>
-      <c r="S49" s="65"/>
-    </row>
-    <row r="50" ht="24" spans="1:19">
+      <c r="R49" s="34"/>
+      <c r="S49" s="57"/>
+    </row>
+    <row r="50" spans="1:19" ht="24">
       <c r="A50" s="2"/>
-      <c r="B50" s="37">
+      <c r="B50" s="35">
         <f t="shared" si="3"/>
         <v>41</v>
       </c>
-      <c r="C50" s="38" t="s">
+      <c r="C50" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="D50" s="39" t="s">
+      <c r="D50" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="E50" s="39" t="s">
+      <c r="E50" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="F50" s="36" t="s">
+      <c r="F50" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G50" s="39" t="s">
+      <c r="G50" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="H50" s="39" t="s">
+      <c r="H50" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="I50" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J50" s="39" t="s">
+      <c r="I50" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" s="37" t="s">
         <v>264</v>
       </c>
-      <c r="K50" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L50" s="39">
+      <c r="K50" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L50" s="37">
         <v>1</v>
       </c>
-      <c r="M50" s="39">
+      <c r="M50" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N50" s="39">
+      <c r="N50" s="37">
         <v>10</v>
       </c>
-      <c r="O50" s="56" t="s">
+      <c r="O50" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P50" s="57">
-        <v>0.0927</v>
-      </c>
-      <c r="Q50" s="57">
+      <c r="P50" s="54">
+        <v>9.2700000000000005E-2</v>
+      </c>
+      <c r="Q50" s="54">
         <f t="shared" si="5"/>
-        <v>0.927</v>
-      </c>
-      <c r="R50" s="39"/>
-      <c r="S50" s="39"/>
-    </row>
-    <row r="51" ht="24" spans="1:19">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="R50" s="37"/>
+      <c r="S50" s="37"/>
+    </row>
+    <row r="51" spans="1:19" ht="24">
       <c r="A51" s="2"/>
-      <c r="B51" s="34">
+      <c r="B51" s="32">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="C51" s="35" t="s">
+      <c r="C51" s="33" t="s">
         <v>265</v>
       </c>
-      <c r="D51" s="36" t="s">
+      <c r="D51" s="34" t="s">
         <v>266</v>
       </c>
-      <c r="E51" s="36" t="s">
+      <c r="E51" s="34" t="s">
         <v>267</v>
       </c>
-      <c r="F51" s="36" t="s">
+      <c r="F51" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G51" s="36" t="s">
+      <c r="G51" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="H51" s="36" t="s">
+      <c r="H51" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I51" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J51" s="36" t="s">
+      <c r="I51" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="K51" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L51" s="36">
+      <c r="K51" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L51" s="34">
         <v>2</v>
       </c>
-      <c r="M51" s="36">
+      <c r="M51" s="34">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N51" s="36">
+      <c r="N51" s="34">
         <v>12</v>
       </c>
-      <c r="O51" s="54" t="s">
+      <c r="O51" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P51" s="55">
-        <v>0.3404</v>
-      </c>
-      <c r="Q51" s="55">
+      <c r="P51" s="52">
+        <v>0.34039999999999998</v>
+      </c>
+      <c r="Q51" s="52">
         <f t="shared" si="5"/>
-        <v>4.0848</v>
-      </c>
-      <c r="R51" s="36"/>
-      <c r="S51" s="65"/>
-    </row>
-    <row r="52" ht="24" spans="1:19">
+        <v>4.0847999999999995</v>
+      </c>
+      <c r="R51" s="34"/>
+      <c r="S51" s="57"/>
+    </row>
+    <row r="52" spans="1:19" ht="36">
       <c r="A52" s="2"/>
-      <c r="B52" s="37">
+      <c r="B52" s="35">
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="C52" s="38" t="s">
+      <c r="C52" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="D52" s="39" t="s">
+      <c r="D52" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="E52" s="39" t="s">
+      <c r="E52" s="37" t="s">
         <v>273</v>
       </c>
-      <c r="F52" s="36" t="s">
+      <c r="F52" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G52" s="39" t="s">
+      <c r="G52" s="37" t="s">
         <v>274</v>
       </c>
-      <c r="H52" s="39" t="s">
+      <c r="H52" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="I52" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J52" s="39" t="s">
+      <c r="I52" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J52" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="K52" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L52" s="39">
+      <c r="K52" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L52" s="37">
         <v>2</v>
       </c>
-      <c r="M52" s="39">
+      <c r="M52" s="37">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N52" s="39">
+      <c r="N52" s="37">
         <v>20</v>
       </c>
-      <c r="O52" s="56" t="s">
+      <c r="O52" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P52" s="57">
-        <v>0.0542</v>
-      </c>
-      <c r="Q52" s="57">
+      <c r="P52" s="54">
+        <v>5.4199999999999998E-2</v>
+      </c>
+      <c r="Q52" s="54">
         <f t="shared" si="5"/>
-        <v>1.084</v>
-      </c>
-      <c r="R52" s="39"/>
-      <c r="S52" s="39"/>
-    </row>
-    <row r="53" ht="28.8" spans="1:19">
+        <v>1.0840000000000001</v>
+      </c>
+      <c r="R52" s="37"/>
+      <c r="S52" s="37"/>
+    </row>
+    <row r="53" spans="1:19" ht="36">
       <c r="A53" s="2"/>
-      <c r="B53" s="34">
+      <c r="B53" s="32">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="C53" s="35" t="s">
+      <c r="C53" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="D53" s="36" t="s">
+      <c r="D53" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="E53" s="36" t="s">
+      <c r="E53" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="F53" s="36" t="s">
+      <c r="F53" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G53" s="36" t="s">
+      <c r="G53" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="H53" s="36" t="s">
+      <c r="H53" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="I53" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J53" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="K53" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L53" s="36">
+      <c r="I53" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J53" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="K53" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L53" s="34">
         <v>1</v>
       </c>
-      <c r="M53" s="36">
+      <c r="M53" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N53" s="36">
+      <c r="N53" s="34">
         <v>6</v>
       </c>
-      <c r="O53" s="54" t="s">
+      <c r="O53" s="51" t="s">
         <v>282</v>
       </c>
-      <c r="P53" s="55">
+      <c r="P53" s="52">
         <v>2.76</v>
       </c>
-      <c r="Q53" s="55">
+      <c r="Q53" s="52">
         <f t="shared" si="5"/>
-        <v>16.56</v>
-      </c>
-      <c r="R53" s="36"/>
-      <c r="S53" s="65"/>
+        <v>16.559999999999999</v>
+      </c>
+      <c r="R53" s="34"/>
+      <c r="S53" s="57"/>
     </row>
     <row r="54" spans="1:19">
       <c r="A54" s="2"/>
-      <c r="B54" s="37">
+      <c r="B54" s="35">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="C54" s="38" t="s">
+      <c r="C54" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="D54" s="39" t="s">
+      <c r="D54" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="E54" s="39" t="s">
+      <c r="E54" s="37" t="s">
         <v>285</v>
       </c>
-      <c r="F54" s="39" t="s">
+      <c r="F54" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="G54" s="39" t="s">
+      <c r="G54" s="37" t="s">
         <v>287</v>
       </c>
-      <c r="H54" s="39" t="s">
+      <c r="H54" s="37" t="s">
         <v>288</v>
       </c>
-      <c r="I54" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J54" s="39" t="s">
+      <c r="I54" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J54" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="K54" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L54" s="39">
+      <c r="K54" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L54" s="37">
         <v>1</v>
       </c>
-      <c r="M54" s="39">
+      <c r="M54" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N54" s="39">
+      <c r="N54" s="37">
         <v>10</v>
       </c>
-      <c r="O54" s="56" t="s">
+      <c r="O54" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P54" s="57">
+      <c r="P54" s="54">
         <v>0.114</v>
       </c>
-      <c r="Q54" s="57">
+      <c r="Q54" s="54">
         <f t="shared" si="5"/>
-        <v>1.14</v>
-      </c>
-      <c r="R54" s="39"/>
-      <c r="S54" s="39"/>
+        <v>1.1400000000000001</v>
+      </c>
+      <c r="R54" s="37"/>
+      <c r="S54" s="37"/>
     </row>
     <row r="55" spans="1:19">
       <c r="A55" s="2"/>
-      <c r="B55" s="34">
+      <c r="B55" s="32">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="C55" s="35" t="s">
+      <c r="C55" s="33" t="s">
         <v>290</v>
       </c>
-      <c r="D55" s="36" t="s">
+      <c r="D55" s="34" t="s">
         <v>291</v>
       </c>
-      <c r="E55" s="36" t="s">
+      <c r="E55" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="F55" s="36" t="s">
+      <c r="F55" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="G55" s="36" t="s">
+      <c r="G55" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="H55" s="39" t="s">
+      <c r="H55" s="37" t="s">
         <v>288</v>
       </c>
-      <c r="I55" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J55" s="36" t="s">
+      <c r="I55" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J55" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="K55" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L55" s="36">
+      <c r="K55" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L55" s="34">
         <v>1</v>
       </c>
-      <c r="M55" s="36">
+      <c r="M55" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N55" s="36">
+      <c r="N55" s="34">
         <v>10</v>
       </c>
-      <c r="O55" s="54" t="s">
+      <c r="O55" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P55" s="55">
-        <v>0.1874</v>
-      </c>
-      <c r="Q55" s="55">
+      <c r="P55" s="52">
+        <v>0.18740000000000001</v>
+      </c>
+      <c r="Q55" s="52">
         <f t="shared" si="5"/>
-        <v>1.874</v>
-      </c>
-      <c r="R55" s="36"/>
-      <c r="S55" s="65"/>
-    </row>
-    <row r="56" ht="24" spans="1:19">
+        <v>1.8740000000000001</v>
+      </c>
+      <c r="R55" s="34"/>
+      <c r="S55" s="57"/>
+    </row>
+    <row r="56" spans="1:19" ht="24">
       <c r="A56" s="2"/>
-      <c r="B56" s="37">
+      <c r="B56" s="35">
         <f t="shared" si="3"/>
         <v>47</v>
       </c>
-      <c r="C56" s="38" t="s">
+      <c r="C56" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="D56" s="39" t="s">
+      <c r="D56" s="37" t="s">
         <v>295</v>
       </c>
-      <c r="E56" s="39" t="s">
+      <c r="E56" s="37" t="s">
         <v>296</v>
       </c>
-      <c r="F56" s="39" t="s">
+      <c r="F56" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="G56" s="39" t="s">
+      <c r="G56" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="H56" s="39" t="s">
+      <c r="H56" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="I56" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J56" s="39" t="s">
+      <c r="I56" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J56" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="K56" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L56" s="39">
+      <c r="K56" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L56" s="37">
         <v>1</v>
       </c>
-      <c r="M56" s="39">
+      <c r="M56" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N56" s="39">
+      <c r="N56" s="37">
         <v>6</v>
       </c>
-      <c r="O56" s="56" t="s">
+      <c r="O56" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P56" s="57">
-        <v>2.3913</v>
-      </c>
-      <c r="Q56" s="57">
+      <c r="P56" s="54">
+        <v>2.3913000000000002</v>
+      </c>
+      <c r="Q56" s="54">
         <f t="shared" si="5"/>
-        <v>14.3478</v>
-      </c>
-      <c r="R56" s="39"/>
-      <c r="S56" s="39"/>
+        <v>14.347800000000001</v>
+      </c>
+      <c r="R56" s="37"/>
+      <c r="S56" s="37"/>
     </row>
     <row r="57" spans="1:19">
       <c r="A57" s="2"/>
-      <c r="B57" s="34">
+      <c r="B57" s="32">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="C57" s="35" t="s">
+      <c r="C57" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="D57" s="36" t="s">
+      <c r="D57" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="E57" s="36" t="s">
+      <c r="E57" s="34" t="s">
         <v>302</v>
       </c>
-      <c r="F57" s="36" t="s">
+      <c r="F57" s="34" t="s">
         <v>303</v>
       </c>
-      <c r="G57" s="36" t="s">
+      <c r="G57" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="H57" s="39" t="s">
+      <c r="H57" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="I57" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J57" s="36" t="s">
+      <c r="I57" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J57" s="34" t="s">
         <v>306</v>
       </c>
-      <c r="K57" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L57" s="36">
+      <c r="K57" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L57" s="34">
         <v>1</v>
       </c>
-      <c r="M57" s="36">
+      <c r="M57" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N57" s="36">
+      <c r="N57" s="34">
         <v>10</v>
       </c>
-      <c r="O57" s="54" t="s">
+      <c r="O57" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P57" s="55">
-        <v>0.0755</v>
-      </c>
-      <c r="Q57" s="55">
+      <c r="P57" s="52">
+        <v>7.5499999999999998E-2</v>
+      </c>
+      <c r="Q57" s="52">
         <f t="shared" si="5"/>
         <v>0.755</v>
       </c>
-      <c r="R57" s="36"/>
-      <c r="S57" s="65"/>
-    </row>
-    <row r="58" ht="24" spans="1:19">
+      <c r="R57" s="34"/>
+      <c r="S57" s="57"/>
+    </row>
+    <row r="58" spans="1:19" ht="24">
       <c r="A58" s="2"/>
-      <c r="B58" s="37">
+      <c r="B58" s="35">
         <f t="shared" si="3"/>
         <v>49</v>
       </c>
-      <c r="C58" s="38" t="s">
+      <c r="C58" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="D58" s="39" t="s">
+      <c r="D58" s="37" t="s">
         <v>307</v>
       </c>
-      <c r="E58" s="39" t="s">
+      <c r="E58" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="F58" s="39" t="s">
+      <c r="F58" s="37" t="s">
         <v>309</v>
       </c>
-      <c r="G58" s="39" t="s">
+      <c r="G58" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="H58" s="39" t="s">
+      <c r="H58" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="I58" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J58" s="39" t="s">
+      <c r="I58" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J58" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K58" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L58" s="39">
+      <c r="K58" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L58" s="37">
         <v>1</v>
       </c>
-      <c r="M58" s="39">
+      <c r="M58" s="37">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N58" s="39">
+      <c r="N58" s="37">
         <v>6</v>
       </c>
-      <c r="O58" s="56" t="s">
+      <c r="O58" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="P58" s="57">
-        <v>1.1384</v>
-      </c>
-      <c r="Q58" s="57">
+      <c r="P58" s="54">
+        <v>1.1384000000000001</v>
+      </c>
+      <c r="Q58" s="54">
         <f t="shared" si="5"/>
-        <v>6.8304</v>
-      </c>
-      <c r="R58" s="39"/>
-      <c r="S58" s="39"/>
+        <v>6.8304000000000009</v>
+      </c>
+      <c r="R58" s="37"/>
+      <c r="S58" s="37"/>
     </row>
     <row r="59" spans="1:19">
       <c r="A59" s="2"/>
-      <c r="B59" s="34">
+      <c r="B59" s="32">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="C59" s="35" t="s">
+      <c r="C59" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="D59" s="36" t="s">
+      <c r="D59" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="E59" s="36" t="s">
+      <c r="E59" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="F59" s="36" t="s">
+      <c r="F59" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="G59" s="36" t="s">
+      <c r="G59" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="H59" s="36" t="s">
+      <c r="H59" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="I59" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J59" s="36" t="s">
+      <c r="I59" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J59" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="K59" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L59" s="36">
+      <c r="K59" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L59" s="34">
         <v>1</v>
       </c>
-      <c r="M59" s="36">
+      <c r="M59" s="34">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="N59" s="36">
+      <c r="N59" s="34">
         <v>10</v>
       </c>
-      <c r="O59" s="54" t="s">
+      <c r="O59" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="P59" s="55">
-        <v>0.2156</v>
-      </c>
-      <c r="Q59" s="55">
+      <c r="P59" s="52">
+        <v>0.21560000000000001</v>
+      </c>
+      <c r="Q59" s="52">
         <f t="shared" si="5"/>
-        <v>2.156</v>
-      </c>
-      <c r="R59" s="36"/>
-      <c r="S59" s="65"/>
-    </row>
-    <row r="60" ht="18.75" spans="1:19">
+        <v>2.1560000000000001</v>
+      </c>
+      <c r="R59" s="34"/>
+      <c r="S59" s="57"/>
+    </row>
+    <row r="60" spans="1:19" ht="36">
       <c r="A60" s="2"/>
-      <c r="B60" s="43"/>
-      <c r="C60" s="44"/>
-      <c r="D60" s="45"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="47"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="47"/>
-      <c r="I60" s="48"/>
-      <c r="J60" s="47"/>
-      <c r="K60" s="48"/>
-      <c r="L60" s="48"/>
-      <c r="M60" s="48"/>
-      <c r="N60" s="59" t="s">
+      <c r="B60" s="32">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="C60" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G60" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="H60" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="I60" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J60" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="K60" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L60" s="34">
+        <v>1</v>
+      </c>
+      <c r="M60" s="34">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N60" s="34">
+        <v>6</v>
+      </c>
+      <c r="O60" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="P60" s="52">
+        <v>0.48049999999999998</v>
+      </c>
+      <c r="Q60" s="52">
+        <f t="shared" si="5"/>
+        <v>2.883</v>
+      </c>
+      <c r="R60" s="34"/>
+      <c r="S60" s="57"/>
+    </row>
+    <row r="61" spans="1:19" ht="36">
+      <c r="A61" s="2"/>
+      <c r="B61" s="32">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="C61" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="D61" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="F61" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="H61" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="I61" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J61" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="K61" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L61" s="34">
+        <v>1</v>
+      </c>
+      <c r="M61" s="34">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N61" s="34">
+        <v>6</v>
+      </c>
+      <c r="O61" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="P61" s="52">
+        <v>0.6825</v>
+      </c>
+      <c r="Q61" s="52">
+        <f t="shared" si="5"/>
+        <v>4.0949999999999998</v>
+      </c>
+      <c r="R61" s="34"/>
+      <c r="S61" s="57"/>
+    </row>
+    <row r="62" spans="1:19" ht="24">
+      <c r="A62" s="2"/>
+      <c r="B62" s="32">
+        <f t="shared" si="3"/>
+        <v>53</v>
+      </c>
+      <c r="C62" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="F62" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="H62" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="I62" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J62" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="K62" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L62" s="34">
+        <v>1</v>
+      </c>
+      <c r="M62" s="34">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N62" s="34">
+        <v>10</v>
+      </c>
+      <c r="O62" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="P62" s="52">
+        <v>0.26019999999999999</v>
+      </c>
+      <c r="Q62" s="52">
+        <f t="shared" si="5"/>
+        <v>2.6019999999999999</v>
+      </c>
+      <c r="R62" s="34"/>
+      <c r="S62" s="57"/>
+    </row>
+    <row r="63" spans="1:19" ht="36">
+      <c r="A63" s="2"/>
+      <c r="B63" s="32">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="C63" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="D63" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="F63" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="H63" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J63" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="K63" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L63" s="34">
+        <v>1</v>
+      </c>
+      <c r="M63" s="34">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N63" s="34">
+        <v>6</v>
+      </c>
+      <c r="O63" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="P63" s="52">
+        <v>2.6</v>
+      </c>
+      <c r="Q63" s="52">
+        <f t="shared" si="5"/>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="R63" s="34"/>
+      <c r="S63" s="57"/>
+    </row>
+    <row r="64" spans="1:19" ht="18.75">
+      <c r="A64" s="2"/>
+      <c r="B64" s="41"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="44"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="45"/>
+      <c r="I64" s="46"/>
+      <c r="J64" s="45"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="46"/>
+      <c r="M64" s="46"/>
+      <c r="N64" s="66" t="s">
         <v>318</v>
       </c>
-      <c r="O60" s="60"/>
-      <c r="P60" s="60"/>
-      <c r="Q60" s="67">
-        <f>SUM(Q10:Q59)</f>
-        <v>111.9872</v>
-      </c>
-      <c r="R60" s="68"/>
-      <c r="S60" s="69"/>
-    </row>
-    <row r="61" ht="18.75" spans="1:19">
-      <c r="A61" s="2"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="50"/>
-      <c r="D61" s="51"/>
-      <c r="E61" s="52"/>
-      <c r="F61" s="52"/>
-      <c r="G61" s="52"/>
-      <c r="H61" s="52"/>
-      <c r="I61" s="52"/>
-      <c r="J61" s="52"/>
-      <c r="K61" s="52"/>
-      <c r="L61" s="52"/>
-      <c r="M61" s="52"/>
-      <c r="N61" s="59" t="s">
+      <c r="O64" s="67"/>
+      <c r="P64" s="67"/>
+      <c r="Q64" s="59">
+        <f>SUM(Q10:Q63)</f>
+        <v>137.16720000000001</v>
+      </c>
+      <c r="R64" s="70"/>
+      <c r="S64" s="71"/>
+    </row>
+    <row r="65" spans="1:19" ht="18.75">
+      <c r="A65" s="2"/>
+      <c r="B65" s="47"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="49"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
+      <c r="H65" s="50"/>
+      <c r="I65" s="50"/>
+      <c r="J65" s="50"/>
+      <c r="K65" s="50"/>
+      <c r="L65" s="50"/>
+      <c r="M65" s="50"/>
+      <c r="N65" s="66" t="s">
         <v>319</v>
       </c>
-      <c r="O61" s="60"/>
-      <c r="P61" s="60"/>
-      <c r="Q61" s="70">
-        <f>Q60/5</f>
-        <v>22.39744</v>
-      </c>
-      <c r="R61" s="71"/>
-      <c r="S61" s="72"/>
+      <c r="O65" s="67"/>
+      <c r="P65" s="67"/>
+      <c r="Q65" s="60">
+        <f>Q64/5</f>
+        <v>27.433440000000001</v>
+      </c>
+      <c r="R65" s="72"/>
+      <c r="S65" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N65:P65"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R60:S61"/>
+    <mergeCell ref="R64:S65"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId2" display="LCSC"/>
-    <hyperlink ref="O11" r:id="rId3" display="LCSC"/>
-    <hyperlink ref="O12" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="O14" r:id="rId5" display="LCSC"/>
-    <hyperlink ref="O15" r:id="rId6" display="LCSC"/>
-    <hyperlink ref="O16" r:id="rId7" display="LCSC"/>
-    <hyperlink ref="O17" r:id="rId8" display="LCSC"/>
-    <hyperlink ref="O18" r:id="rId9" display="LCSC"/>
-    <hyperlink ref="O20" r:id="rId10" display="LCSC"/>
-    <hyperlink ref="O21" r:id="rId11" display="LCSC"/>
-    <hyperlink ref="O22" r:id="rId12" display="LCSC"/>
-    <hyperlink ref="O23" r:id="rId13" display="LCSC"/>
-    <hyperlink ref="O24" r:id="rId14" display="LCSC"/>
-    <hyperlink ref="O25" r:id="rId15" display="LCSC"/>
-    <hyperlink ref="O26" r:id="rId13" display="LCSC"/>
-    <hyperlink ref="O28" r:id="rId16" display="LCSC"/>
-    <hyperlink ref="O30" r:id="rId17" display="LCSC"/>
-    <hyperlink ref="O31" r:id="rId18" display="LCSC"/>
-    <hyperlink ref="O32" r:id="rId19" display="LCSC"/>
-    <hyperlink ref="O33" r:id="rId20" display="LCSC"/>
-    <hyperlink ref="O35" r:id="rId21" display="LCSC"/>
-    <hyperlink ref="O36" r:id="rId22" display="LCSC"/>
-    <hyperlink ref="O37" r:id="rId23" display="LCSC"/>
-    <hyperlink ref="O38" r:id="rId24" display="LCSC"/>
-    <hyperlink ref="O39" r:id="rId25" display="LCSC"/>
-    <hyperlink ref="O40" r:id="rId26" display="LCSC"/>
-    <hyperlink ref="O41" r:id="rId27" display="LCSC"/>
-    <hyperlink ref="O42" r:id="rId28" display="LCSC"/>
-    <hyperlink ref="O43" r:id="rId29" display="LCSC"/>
-    <hyperlink ref="O44" r:id="rId30" display="LCSC"/>
-    <hyperlink ref="O45" r:id="rId31" display="LCSC"/>
-    <hyperlink ref="O46" r:id="rId32" display="LCSC"/>
-    <hyperlink ref="O47" r:id="rId33" display="LSCS"/>
-    <hyperlink ref="O49" r:id="rId34" display="LCSC"/>
-    <hyperlink ref="O50" r:id="rId35" display="LCSC"/>
-    <hyperlink ref="O51" r:id="rId36" display="LCSC"/>
-    <hyperlink ref="O52" r:id="rId37" display="LCSC"/>
-    <hyperlink ref="O54" r:id="rId38" display="LCSC"/>
-    <hyperlink ref="O56" r:id="rId39" display="LCSC"/>
-    <hyperlink ref="O58" r:id="rId40" display="LCSC"/>
-    <hyperlink ref="O59" r:id="rId41" display="LCSC"/>
-    <hyperlink ref="O13" r:id="rId42" display="LCSC"/>
-    <hyperlink ref="O34" r:id="rId43" display="LCSC"/>
-    <hyperlink ref="O48" r:id="rId44" display="LCSC"/>
-    <hyperlink ref="O53" r:id="rId45" display="Aliexpress"/>
-    <hyperlink ref="O55" r:id="rId46" display="LCSC"/>
-    <hyperlink ref="O19" r:id="rId47" display="LCSC"/>
-    <hyperlink ref="O57" r:id="rId48" display="LCSC"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O17" r:id="rId7"/>
+    <hyperlink ref="O18" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O22" r:id="rId11"/>
+    <hyperlink ref="O23" r:id="rId12"/>
+    <hyperlink ref="O24" r:id="rId13"/>
+    <hyperlink ref="O25" r:id="rId14"/>
+    <hyperlink ref="O26" r:id="rId15"/>
+    <hyperlink ref="O28" r:id="rId16"/>
+    <hyperlink ref="O30" r:id="rId17"/>
+    <hyperlink ref="O31" r:id="rId18"/>
+    <hyperlink ref="O32" r:id="rId19"/>
+    <hyperlink ref="O33" r:id="rId20"/>
+    <hyperlink ref="O35" r:id="rId21"/>
+    <hyperlink ref="O36" r:id="rId22"/>
+    <hyperlink ref="O37" r:id="rId23"/>
+    <hyperlink ref="O38" r:id="rId24"/>
+    <hyperlink ref="O39" r:id="rId25"/>
+    <hyperlink ref="O40" r:id="rId26"/>
+    <hyperlink ref="O41" r:id="rId27"/>
+    <hyperlink ref="O42" r:id="rId28"/>
+    <hyperlink ref="O43" r:id="rId29"/>
+    <hyperlink ref="O44" r:id="rId30"/>
+    <hyperlink ref="O45" r:id="rId31"/>
+    <hyperlink ref="O46" r:id="rId32"/>
+    <hyperlink ref="O47" r:id="rId33"/>
+    <hyperlink ref="O49" r:id="rId34"/>
+    <hyperlink ref="O50" r:id="rId35"/>
+    <hyperlink ref="O51" r:id="rId36"/>
+    <hyperlink ref="O52" r:id="rId37"/>
+    <hyperlink ref="O54" r:id="rId38"/>
+    <hyperlink ref="O56" r:id="rId39"/>
+    <hyperlink ref="O58" r:id="rId40"/>
+    <hyperlink ref="O59" r:id="rId41"/>
+    <hyperlink ref="O13" r:id="rId42"/>
+    <hyperlink ref="O34" r:id="rId43"/>
+    <hyperlink ref="O48" r:id="rId44"/>
+    <hyperlink ref="O53" r:id="rId45"/>
+    <hyperlink ref="O55" r:id="rId46"/>
+    <hyperlink ref="O19" r:id="rId47"/>
+    <hyperlink ref="O57" r:id="rId48"/>
+    <hyperlink ref="O60" r:id="rId49"/>
+    <hyperlink ref="O61" r:id="rId50"/>
+    <hyperlink ref="O62" r:id="rId51"/>
+    <hyperlink ref="O63" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId53"/>
 </worksheet>
 </file>
--- a/Design-Files/Deliverables/BOM/eSpark BOM.xlsx
+++ b/Design-Files/Deliverables/BOM/eSpark BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="334">
   <si>
     <t>Component list</t>
   </si>
@@ -1021,9 +1021,6 @@
   </si>
   <si>
     <t>High sensitivity wireless remote control receiving module RXB61 multiple frequency 315M.433MHZ</t>
-  </si>
-  <si>
-    <t>Alibaba</t>
   </si>
 </sst>
 </file>
@@ -1031,9 +1028,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1542,7 +1539,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1614,16 +1611,16 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1635,10 +1632,10 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5278,17 +5275,17 @@
         <v>5</v>
       </c>
       <c r="N63" s="34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O63" s="51" t="s">
-        <v>334</v>
+        <v>282</v>
       </c>
       <c r="P63" s="52">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="52">
         <f t="shared" si="5"/>
-        <v>15.600000000000001</v>
+        <v>10</v>
       </c>
       <c r="R63" s="34"/>
       <c r="S63" s="57"/>
@@ -5314,7 +5311,7 @@
       <c r="P64" s="67"/>
       <c r="Q64" s="59">
         <f>SUM(Q10:Q63)</f>
-        <v>137.16720000000001</v>
+        <v>131.56720000000001</v>
       </c>
       <c r="R64" s="70"/>
       <c r="S64" s="71"/>
@@ -5340,7 +5337,7 @@
       <c r="P65" s="67"/>
       <c r="Q65" s="60">
         <f>Q64/5</f>
-        <v>27.433440000000001</v>
+        <v>26.313440000000003</v>
       </c>
       <c r="R65" s="72"/>
       <c r="S65" s="73"/>
